--- a/paper_prep/tuning_ref.xlsx
+++ b/paper_prep/tuning_ref.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srd2\Code\nonCUI_bulldozer_blade_control\paper_prep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269BD168-6FD4-4A34-92CF-2903690F831F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8242C8-AFB9-46F7-9AEF-D2772D083EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -118,25 +118,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -444,7 +429,7 @@
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
         <v>0.1</v>
       </c>
       <c r="C2" s="1">
@@ -462,7 +447,7 @@
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="1">
         <v>1</v>
       </c>
       <c r="C3" s="1">
@@ -480,7 +465,7 @@
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="1">
         <v>5</v>
       </c>
       <c r="C4">
@@ -498,7 +483,7 @@
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="1">
         <v>7.5</v>
       </c>
       <c r="C5">
@@ -516,7 +501,7 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="1">
         <v>10</v>
       </c>
       <c r="C6" s="1">
@@ -534,7 +519,7 @@
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="1">
         <v>15</v>
       </c>
       <c r="C7" s="1">
@@ -552,16 +537,16 @@
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="3">
         <v>20</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <v>5.5068122901692003E-2</v>
       </c>
-      <c r="D8" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="D8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="3">
         <f t="shared" si="0"/>
         <v>0.25506812290169201</v>
       </c>
@@ -570,7 +555,7 @@
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="1">
         <v>25</v>
       </c>
       <c r="C9">
@@ -588,7 +573,7 @@
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="1">
         <v>30</v>
       </c>
       <c r="C10">
@@ -606,7 +591,7 @@
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="1">
         <v>35</v>
       </c>
       <c r="C11">
@@ -624,7 +609,7 @@
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="1">
         <v>40</v>
       </c>
       <c r="C12" s="1">
@@ -642,7 +627,7 @@
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="1">
         <v>45</v>
       </c>
       <c r="C13">
@@ -660,7 +645,7 @@
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="1">
         <v>50</v>
       </c>
       <c r="C14" s="1">
@@ -678,7 +663,7 @@
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="1">
         <v>100</v>
       </c>
       <c r="C15" s="1">
@@ -699,7 +684,7 @@
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="2">
         <v>0.05</v>
       </c>
       <c r="C17" s="2">
@@ -717,7 +702,7 @@
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="2">
         <v>0.1</v>
       </c>
       <c r="C18" s="2">
@@ -735,7 +720,7 @@
       <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="2">
         <v>0.2</v>
       </c>
       <c r="C19" s="2">
@@ -753,7 +738,7 @@
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="2">
         <v>0.25</v>
       </c>
       <c r="C20" s="2">
@@ -771,16 +756,16 @@
       <c r="A21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="5">
         <v>0.3</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="5">
         <v>5.3451543291111001E-2</v>
       </c>
-      <c r="D21" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="D21" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E21" s="3">
         <f t="shared" si="1"/>
         <v>0.25345154329111103</v>
       </c>
@@ -789,7 +774,7 @@
       <c r="A22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="4">
+      <c r="B22" s="2">
         <v>0.35</v>
       </c>
       <c r="C22" s="2">
@@ -807,7 +792,7 @@
       <c r="A23" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="4">
+      <c r="B23" s="2">
         <v>0.4</v>
       </c>
       <c r="C23" s="2">
@@ -830,7 +815,7 @@
       <c r="A25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="2">
         <v>0.5</v>
       </c>
       <c r="C25" s="2">
@@ -848,7 +833,7 @@
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26" s="2">
         <v>0.25</v>
       </c>
       <c r="C26">
@@ -866,7 +851,7 @@
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="1">
         <v>0.125</v>
       </c>
       <c r="C27">
@@ -884,7 +869,7 @@
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28" s="2">
         <v>6.25E-2</v>
       </c>
       <c r="C28" s="2">
@@ -906,7 +891,7 @@
       <c r="A30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="4">
+      <c r="B30" s="2">
         <v>0.1</v>
       </c>
       <c r="C30">
@@ -993,19 +978,19 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="10">
-        <v>5</v>
-      </c>
-      <c r="C35" s="10">
+      <c r="A35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="5">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5">
         <v>5.3224357519920003E-2</v>
       </c>
-      <c r="D35" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="E35" s="8">
+      <c r="D35" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E35" s="3">
         <f t="shared" si="1"/>
         <v>0.25322435751992001</v>
       </c>
@@ -1115,7 +1100,7 @@
         <v>0.2</v>
       </c>
       <c r="E42" s="1">
-        <f t="shared" ref="E41:E42" si="2">C42+D42</f>
+        <f t="shared" ref="E42" si="2">C42+D42</f>
         <v>0.25120797325863103</v>
       </c>
     </row>

--- a/paper_prep/tuning_ref.xlsx
+++ b/paper_prep/tuning_ref.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srd2\Code\nonCUI_bulldozer_blade_control\paper_prep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4272584-1058-4E3E-A1E0-64E725800889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343C81D4-A3C5-490E-A9ED-02882A2DBD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
   <si>
     <t>Controller</t>
   </si>
@@ -84,14 +84,58 @@
   </si>
   <si>
     <t>Fzy PI</t>
+  </si>
+  <si>
+    <t>3+</t>
+  </si>
+  <si>
+    <t>Fzy PID</t>
+  </si>
+  <si>
+    <t>Fzy (Prop)</t>
+  </si>
+  <si>
+    <t>Kp</t>
+  </si>
+  <si>
+    <t>Ki</t>
+  </si>
+  <si>
+    <t>Kd</t>
+  </si>
+  <si>
+    <t>Parameters</t>
+  </si>
+  <si>
+    <t>RMSE Yaw (m radians)</t>
+  </si>
+  <si>
+    <t>RMSE Depth (mm)</t>
+  </si>
+  <si>
+    <t>Corner 1 (m)</t>
+  </si>
+  <si>
+    <t>Corner 2 (m)</t>
+  </si>
+  <si>
+    <t>RMSE Roll (m radians)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -125,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -140,11 +184,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -427,10 +470,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,38 +516,102 @@
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1">
         <v>2.21971231355823</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="1">
         <v>4.7080959047163304</v>
       </c>
-      <c r="I2" s="6">
-        <f>G2+H2</f>
+      <c r="I2" s="1">
+        <f t="shared" ref="I2:I8" si="0">G2+H2</f>
         <v>6.9278082182745599</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2">
+        <v>2.6254520105064398</v>
+      </c>
+      <c r="M2" s="2">
+        <v>4.3689033669234201</v>
+      </c>
+      <c r="N2" s="2">
+        <v>2.6254520105064398</v>
+      </c>
+      <c r="O2" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2">
+        <v>3</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" s="1"/>
+      <c r="V2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -515,41 +637,107 @@
         <v>4.5903422097573197</v>
       </c>
       <c r="I3" s="1">
-        <f>G3+H3</f>
+        <f t="shared" si="0"/>
         <v>6.8987173729876998</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2">
+        <v>2.70647393637041</v>
+      </c>
+      <c r="M3" s="2">
+        <v>4.3642736851896498</v>
+      </c>
+      <c r="N3" s="2">
+        <v>2.70647393637041</v>
+      </c>
+      <c r="O3" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="R3" s="2">
+        <v>3</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6">
-        <v>2</v>
-      </c>
-      <c r="C4" s="6">
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
         <v>4.7</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="7">
+      <c r="D4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4">
         <v>2.1960609734291201</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4">
         <v>4.5073075200186103</v>
       </c>
-      <c r="I4" s="6">
-        <f>G4+H4</f>
+      <c r="I4" s="1">
+        <f t="shared" si="0"/>
         <v>6.70336849344773</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="1">
+        <v>2.6838922728213102</v>
+      </c>
+      <c r="M4" s="1">
+        <v>4.3000247353851897</v>
+      </c>
+      <c r="N4" s="1">
+        <v>2.6838922728213102</v>
+      </c>
+      <c r="O4" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="R4" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="S4" s="2">
+        <v>4</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -575,11 +763,44 @@
         <v>4.5026500082107601</v>
       </c>
       <c r="I5" s="1">
-        <f>G5+H5</f>
+        <f t="shared" si="0"/>
         <v>6.70339463475388</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="1">
+        <v>2.6838045064445302</v>
+      </c>
+      <c r="M5" s="1">
+        <v>4.2997037019432103</v>
+      </c>
+      <c r="N5" s="1">
+        <v>2.6838045064445302</v>
+      </c>
+      <c r="O5" s="2">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="1">
+        <v>15</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -605,11 +826,44 @@
         <v>4.2538489701498401</v>
       </c>
       <c r="I6" s="1">
-        <f>G6+H6</f>
+        <f t="shared" si="0"/>
         <v>6.6057322753628505</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2">
+        <v>2.53600949634829</v>
+      </c>
+      <c r="M6" s="2">
+        <v>4.3923222375319098</v>
+      </c>
+      <c r="N6" s="2">
+        <v>2.53600949634829</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3</v>
+      </c>
+      <c r="S6" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -635,523 +889,291 @@
         <v>4.1622551570020097</v>
       </c>
       <c r="I7" s="3">
-        <f>G7+H7</f>
+        <f t="shared" si="0"/>
         <v>6.5856334215489598</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="K7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="6">
+        <v>2.6263871457176302</v>
+      </c>
+      <c r="M7" s="6">
+        <v>4.1650818919877501</v>
+      </c>
+      <c r="N7" s="6">
+        <v>2.6263871457176302</v>
+      </c>
+      <c r="O7" s="7">
+        <v>2</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="R7" s="2">
+        <v>325</v>
+      </c>
+      <c r="S7" s="2">
+        <v>6</v>
+      </c>
+      <c r="T7" s="2">
+        <v>6</v>
+      </c>
+      <c r="U7" s="2">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="1">
         <v>325</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="2">
         <v>4</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="1">
         <v>100</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="F8" s="6">
-        <v>2</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
         <v>2.0980078086123899</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="1">
         <v>4.4885744324294503</v>
       </c>
-      <c r="I8" s="6">
-        <f>G8+H8</f>
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
         <v>6.5865822410418406</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="2">
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="2">
         <v>3</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="2">
-        <v>2.6254520105064398</v>
-      </c>
-      <c r="H14" s="8">
-        <v>4.3689033669234201</v>
-      </c>
-      <c r="I14" s="1">
-        <f>H14+G14</f>
-        <v>6.9943553774298604</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="2">
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="K16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="5">
+        <v>15</v>
+      </c>
+      <c r="C23" s="5">
+        <v>31</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="3">
         <v>0.2</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="2">
-        <v>2.7455782527980799</v>
-      </c>
-      <c r="H15" s="8">
-        <v>4.3632582225448102</v>
-      </c>
-      <c r="I15" s="1">
-        <f t="shared" ref="I15:I18" si="0">H15+G15</f>
-        <v>7.1088364753428905</v>
-      </c>
-      <c r="K15" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="8">
-        <v>3.1</v>
-      </c>
-      <c r="C16" s="8">
-        <v>4</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G16" s="6">
-        <v>2.6437402018685998</v>
-      </c>
-      <c r="H16" s="7">
-        <v>4.3000247353851897</v>
-      </c>
-      <c r="I16" s="6">
-        <f t="shared" si="0"/>
-        <v>6.9437649372537891</v>
-      </c>
-      <c r="K16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="6">
-        <v>3</v>
-      </c>
-      <c r="C17" s="6">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="6">
-        <v>2.6838922728213102</v>
-      </c>
-      <c r="H17" s="6">
-        <v>4.2997037019432103</v>
-      </c>
-      <c r="I17" s="6">
-        <f t="shared" si="0"/>
-        <v>6.9835959747645209</v>
-      </c>
-      <c r="K17" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="6">
-        <v>15</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="7">
-        <v>2.6263871457176302</v>
-      </c>
-      <c r="H18" s="7">
-        <v>4.1650818919877501</v>
-      </c>
-      <c r="I18" s="6">
-        <f>G18+H18</f>
-        <v>6.7914690377053804</v>
-      </c>
-      <c r="K18" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5">
-        <v>15</v>
-      </c>
-      <c r="C19" s="5">
-        <v>31</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" s="5">
+      <c r="F23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="5">
         <v>2.6413115876657098</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H23" s="4">
         <v>4.0724643310900799</v>
       </c>
-      <c r="I19" s="3">
-        <f>G19+H19</f>
+      <c r="I23" s="3">
+        <f>G23+H23</f>
         <v>6.7137759187557897</v>
       </c>
-      <c r="K19" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="8">
-        <v>325</v>
-      </c>
-      <c r="C20" s="8">
-        <v>6</v>
-      </c>
-      <c r="D20" s="8">
-        <v>6</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8">
-        <v>2</v>
-      </c>
-      <c r="G20" s="8">
-        <v>2.53600949634829</v>
-      </c>
-      <c r="H20" s="8">
-        <v>4.3923222375319098</v>
-      </c>
-      <c r="I20" s="1">
-        <f t="shared" ref="I20" si="1">H20+G20</f>
-        <v>6.9283317338801993</v>
-      </c>
-      <c r="K20" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="2"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/paper_prep/tuning_ref.xlsx
+++ b/paper_prep/tuning_ref.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srd2\Code\nonCUI_bulldozer_blade_control\paper_prep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{343C81D4-A3C5-490E-A9ED-02882A2DBD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79E29B2-815E-472A-A9A8-C640C4BDBEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="28">
   <si>
     <t>Controller</t>
   </si>
@@ -977,67 +977,82 @@
       <c r="K11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
+      <c r="L11" s="2">
+        <v>0.54174885225125102</v>
+      </c>
+      <c r="M11" s="2">
+        <v>3.25089009406955</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0.54174885225125102</v>
+      </c>
       <c r="O11" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="K12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0.52345382659378403</v>
+      </c>
+      <c r="M12" s="1">
+        <v>3.1411064173451901</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0.52345382659378403</v>
+      </c>
       <c r="O12" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
+      <c r="K13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1.65765470453266</v>
+      </c>
+      <c r="M13" s="1">
+        <v>4.8853121964548096</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1.65765470453266</v>
+      </c>
       <c r="O13" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="2">
-        <v>2</v>
+      <c r="K14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="2">
+        <v>0.57005417203762998</v>
+      </c>
+      <c r="M14" s="1">
+        <v>3.6471083147947998</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0.57005417203762998</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K15" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
       <c r="N15" s="1"/>
-      <c r="O15" s="2">
-        <v>3</v>
-      </c>
+      <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K16" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="K16" s="2"/>
       <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+      <c r="M16" s="1"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="O16" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>

--- a/paper_prep/tuning_ref.xlsx
+++ b/paper_prep/tuning_ref.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srd2\Code\nonCUI_bulldozer_blade_control\paper_prep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79E29B2-815E-472A-A9A8-C640C4BDBEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69969DCB-020A-47CF-8BD0-2B381F3CDFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="26">
   <si>
     <t>Controller</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Fzy PI</t>
   </si>
   <si>
-    <t>3+</t>
-  </si>
-  <si>
     <t>Fzy PID</t>
   </si>
   <si>
@@ -102,9 +99,6 @@
   </si>
   <si>
     <t>Kd</t>
-  </si>
-  <si>
-    <t>Parameters</t>
   </si>
   <si>
     <t>RMSE Yaw (m radians)</t>
@@ -126,6 +120,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -169,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -185,10 +182,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -470,7 +470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -481,14 +481,13 @@
     <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
     <col min="18" max="20" width="4" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -520,37 +519,17 @@
         <v>0</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O1" s="2"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -582,36 +561,18 @@
       <c r="K2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="7">
         <v>2.6254520105064398</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="7">
         <v>4.3689033669234201</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="7">
         <v>2.6254520105064398</v>
       </c>
-      <c r="O2" s="2">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" s="2">
-        <v>3</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="U2" s="1"/>
-      <c r="V2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -641,40 +602,20 @@
         <v>6.8987173729876998</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="2">
-        <v>2.70647393637041</v>
-      </c>
-      <c r="M3" s="2">
-        <v>4.3642736851896498</v>
-      </c>
-      <c r="N3" s="2">
-        <v>2.70647393637041</v>
-      </c>
-      <c r="O3" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R3" s="2">
-        <v>3</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" s="2">
-        <v>0.2</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="L3" s="8">
+        <v>2.6838922728213102</v>
+      </c>
+      <c r="M3" s="8">
+        <v>4.3000247353851897</v>
+      </c>
+      <c r="N3" s="8">
+        <v>2.6838922728213102</v>
+      </c>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -704,40 +645,32 @@
         <v>6.70336849344773</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L4" s="1">
-        <v>2.6838922728213102</v>
-      </c>
-      <c r="M4" s="1">
-        <v>4.3000247353851897</v>
-      </c>
-      <c r="N4" s="1">
-        <v>2.6838922728213102</v>
-      </c>
-      <c r="O4" s="2">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R4" s="2">
-        <v>3.1</v>
-      </c>
-      <c r="S4" s="2">
-        <v>4</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="L4" s="7">
+        <v>2.53600949634829</v>
+      </c>
+      <c r="M4" s="7">
+        <v>4.3923222375319098</v>
+      </c>
+      <c r="N4" s="7">
+        <v>2.53600949634829</v>
+      </c>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="7">
+        <v>2.70647393637041</v>
+      </c>
+      <c r="R4" s="7">
+        <v>4.3642736851896498</v>
+      </c>
+      <c r="S4" s="7">
+        <v>2.70647393637041</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -767,40 +700,32 @@
         <v>6.70339463475388</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="8">
+        <v>2.6263871457176302</v>
+      </c>
+      <c r="M5" s="8">
+        <v>4.1650818919877501</v>
+      </c>
+      <c r="N5" s="8">
+        <v>2.6263871457176302</v>
+      </c>
+      <c r="O5" s="2"/>
+      <c r="P5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="1">
+      <c r="Q5" s="8">
         <v>2.6838045064445302</v>
       </c>
-      <c r="M5" s="1">
+      <c r="R5" s="8">
         <v>4.2997037019432103</v>
       </c>
-      <c r="N5" s="1">
+      <c r="S5" s="8">
         <v>2.6838045064445302</v>
       </c>
-      <c r="O5" s="2">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R5" s="1">
-        <v>15</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="U5" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -829,41 +754,9 @@
         <f t="shared" si="0"/>
         <v>6.6057322753628505</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="2">
-        <v>2.53600949634829</v>
-      </c>
-      <c r="M6" s="2">
-        <v>4.3923222375319098</v>
-      </c>
-      <c r="N6" s="2">
-        <v>2.53600949634829</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R6" s="1">
-        <v>3</v>
-      </c>
-      <c r="S6" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -893,40 +786,20 @@
         <v>6.5856334215489598</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="6">
-        <v>2.6263871457176302</v>
-      </c>
-      <c r="M7" s="6">
-        <v>4.1650818919877501</v>
-      </c>
-      <c r="N7" s="6">
-        <v>2.6263871457176302</v>
-      </c>
-      <c r="O7" s="7">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="R7" s="2">
-        <v>325</v>
-      </c>
-      <c r="S7" s="2">
-        <v>6</v>
-      </c>
-      <c r="T7" s="2">
-        <v>6</v>
-      </c>
-      <c r="U7" s="2">
-        <v>1</v>
-      </c>
-      <c r="V7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="6"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -955,120 +828,155 @@
         <f t="shared" si="0"/>
         <v>6.5865822410418406</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K10" s="1" t="s">
+      <c r="K8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="8">
+        <v>2.60799281255361</v>
+      </c>
+      <c r="M8" s="8">
+        <v>4.7666636713485904</v>
+      </c>
+      <c r="N8" s="8">
+        <v>2.60799281255361</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="8">
+        <v>2.7039812466735502</v>
+      </c>
+      <c r="M9" s="8">
+        <v>4.6626291594227602</v>
+      </c>
+      <c r="N9" s="8">
+        <v>2.7039812466735502</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="8">
+        <v>2.9287489468988701</v>
+      </c>
+      <c r="M10" s="8">
+        <v>4.8573097215334604</v>
+      </c>
+      <c r="N10" s="8">
+        <v>2.9287489468988701</v>
+      </c>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="8">
+        <v>2.5799036088813798</v>
+      </c>
+      <c r="M11" s="8">
+        <v>4.3907732926693104</v>
+      </c>
+      <c r="N11" s="8">
+        <v>2.5799036088813798</v>
+      </c>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="2" t="s">
+      <c r="L13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K11" s="2" t="s">
+      <c r="N13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L14" s="7">
         <v>0.54174885225125102</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M14" s="7">
         <v>3.25089009406955</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N14" s="7">
         <v>0.54174885225125102</v>
       </c>
-      <c r="O11" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K12" s="2" t="s">
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L15" s="8">
         <v>0.52345382659378403</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M15" s="8">
         <v>3.1411064173451901</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N15" s="8">
         <v>0.52345382659378403</v>
       </c>
-      <c r="O12" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" s="1">
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="K16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="7">
+        <v>0.57005417203762998</v>
+      </c>
+      <c r="M16" s="8">
+        <v>3.6471083147947998</v>
+      </c>
+      <c r="N16" s="7">
+        <v>0.57005417203762998</v>
+      </c>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="8">
         <v>1.65765470453266</v>
       </c>
-      <c r="M13" s="1">
+      <c r="M17" s="8">
         <v>4.8853121964548096</v>
       </c>
-      <c r="N13" s="1">
+      <c r="N17" s="8">
         <v>1.65765470453266</v>
       </c>
-      <c r="O13" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="2">
-        <v>0.57005417203762998</v>
-      </c>
-      <c r="M14" s="1">
-        <v>3.6471083147947998</v>
-      </c>
-      <c r="N14" s="2">
-        <v>0.57005417203762998</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="2"/>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
@@ -1098,29 +1006,125 @@
         <v>6.7137759187557897</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2">
+        <v>3</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O26" s="1"/>
+      <c r="P26" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L27" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="M27" s="2">
+        <v>4</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L28" s="2">
+        <v>325</v>
+      </c>
+      <c r="M28" s="2">
+        <v>6</v>
+      </c>
+      <c r="N28" s="2">
+        <v>6</v>
+      </c>
+      <c r="O28" s="2">
+        <v>1</v>
+      </c>
+      <c r="P28" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="K30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30" s="1">
+        <v>15</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O30" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
